--- a/project/Budget.xlsx
+++ b/project/Budget.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Staff" sheetId="1" state="visible" r:id="rId3"/>
@@ -331,7 +331,7 @@
     <t xml:space="preserve">State of the art</t>
   </si>
   <si>
-    <t xml:space="preserve">Search and final bake</t>
+    <t xml:space="preserve">Search and analysis</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Researcher 1</t>
@@ -2715,7 +2715,7 @@
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
       <c r="L21" s="11" t="n">
-        <f aca="false">K22</f>
+        <f aca="false">K22+K24+K26</f>
         <v>2190</v>
       </c>
       <c r="M21" s="11"/>
@@ -2735,8 +2735,8 @@
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11" t="n">
-        <f aca="false">J23+J25+J27</f>
-        <v>2190</v>
+        <f aca="false">J23</f>
+        <v>990</v>
       </c>
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
@@ -2783,7 +2783,10 @@
       <c r="H24" s="13"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
+      <c r="K24" s="11" t="n">
+        <f aca="false">J25</f>
+        <v>300</v>
+      </c>
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
     </row>
@@ -2829,7 +2832,10 @@
       <c r="H26" s="13"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
+      <c r="K26" s="11" t="n">
+        <f aca="false">J27</f>
+        <v>900</v>
+      </c>
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
     </row>
@@ -4742,7 +4748,7 @@
       </c>
       <c r="E13" s="26" t="n">
         <f aca="false">Summary!C9*E12</f>
-        <v>295.419049091713</v>
+        <v>295.419049091712</v>
       </c>
       <c r="F13" s="8"/>
     </row>
